--- a/data/trans_orig/P25C_R2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) en 2023</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>472</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108932</t>
+          <t>109053</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113994</t>
+          <t>114040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45317</t>
+          <t>46582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157675</t>
+          <t>157599</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162805</t>
+          <t>162745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386161</t>
+          <t>385550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>398690</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74518</t>
+          <t>74776</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81174</t>
+          <t>81335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>462195</t>
+          <t>461450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>480701</t>
+          <t>480806</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133920</t>
+          <t>134086</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140783</t>
+          <t>140771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67329</t>
+          <t>67989</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74183</t>
+          <t>74201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205511</t>
+          <t>205044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214343</t>
+          <t>214066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184634</t>
+          <t>183890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192542</t>
+          <t>192368</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119608</t>
+          <t>119524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127063</t>
+          <t>127415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307184</t>
+          <t>307522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317896</t>
+          <t>318262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39386</t>
+          <t>39568</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>825428</t>
+          <t>825958</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>844555</t>
+          <t>844082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>317645</t>
+          <t>318278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>329169</t>
+          <t>329494</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1147610</t>
+          <t>1147428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1173904</t>
+          <t>1173753</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C_R2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R2_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>565</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>112316</t>
+          <t>120242</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109053</t>
+          <t>115993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114040</t>
+          <t>122117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48612</t>
+          <t>52291</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46582</t>
+          <t>50484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>160928</t>
+          <t>172533</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157599</t>
+          <t>168531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162745</t>
+          <t>174733</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>122827</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>122827</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>122827</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>163696</t>
+          <t>175682</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>163696</t>
+          <t>175682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>163696</t>
+          <t>175682</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20857</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>394944</t>
+          <t>166708</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385550</t>
+          <t>161723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>398690</t>
+          <t>169378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>78856</t>
+          <t>85367</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74776</t>
+          <t>80857</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81335</t>
+          <t>87800</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>473799</t>
+          <t>252075</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>461450</t>
+          <t>246550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>480806</t>
+          <t>256306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>171000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>171000</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>171000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>90061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>90061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>90061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>482307</t>
+          <t>261061</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>482307</t>
+          <t>261061</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>482307</t>
+          <t>261061</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>8079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,22 +1446,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11199</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>138655</t>
+          <t>161700</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134086</t>
+          <t>156456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140771</t>
+          <t>163844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72358</t>
+          <t>80513</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67989</t>
+          <t>76069</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74201</t>
+          <t>82884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>211012</t>
+          <t>242212</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205044</t>
+          <t>235509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214066</t>
+          <t>245674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>141392</t>
+          <t>164535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>141392</t>
+          <t>164535</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141392</t>
+          <t>164535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>74851</t>
+          <t>83610</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74851</t>
+          <t>83610</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74851</t>
+          <t>83610</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>216243</t>
+          <t>248145</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>216243</t>
+          <t>248145</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>216243</t>
+          <t>248145</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>189476</t>
+          <t>196639</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183890</t>
+          <t>190952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192368</t>
+          <t>199713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>124395</t>
+          <t>133188</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119524</t>
+          <t>128091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127415</t>
+          <t>136645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>313870</t>
+          <t>329827</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307522</t>
+          <t>323800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318262</t>
+          <t>334923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>130044</t>
+          <t>139363</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>130044</t>
+          <t>139363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>130044</t>
+          <t>139363</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>324749</t>
+          <t>341220</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>324749</t>
+          <t>341220</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>324749</t>
+          <t>341220</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>21661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39568</t>
+          <t>40124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>835390</t>
+          <t>645289</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>825958</t>
+          <t>636746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>844082</t>
+          <t>650992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>324220</t>
+          <t>351359</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>318278</t>
+          <t>344510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>329494</t>
+          <t>356698</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1159610</t>
+          <t>996648</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1147428</t>
+          <t>985985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1173753</t>
+          <t>1004448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
